--- a/Central_Comparison_Table.xlsx
+++ b/Central_Comparison_Table.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Central Comparison Table'!$A$1:$M$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Central Comparison Table'!$A$1:$N$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -467,13 +467,14 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="46" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -509,35 +510,40 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Sample size</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>cM/Mb</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>cM/Mb status</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Gini (raw/unbinned)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Gini status</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>NCO rate (bp-1 gen-1) / count</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>CO count or genetic map length</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Notes / caveats</t>
         </is>
@@ -574,33 +580,38 @@
           <t>Stevison et al. 2016 MBE</t>
         </is>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>13 individuals</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="n">
         <v>0.6893</v>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Computed using an independent Ne=23,230 (Han et al. 2024 Curr Biol, common-ancestor point estimate from a 3-population bonobo demographic model, cross-validated against Kuhlwilm et al. and the prior literature range 5,000-29,129) rather than the paper's own ~1.193 cM/Mb, which is circular (back-solved to force equality across all 3 species). A genuine point estimate from a dedicated demographic study was preferred over the midpoint of the wider Prado-Martinez et al. 2013 range (17,850).</t>
         </is>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="J2" s="3" t="n">
         <v>0.8128</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>independent (raw/unbinned)</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>ρ/kb = 0.6405</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>ρ/kb independently validated against the published value (&lt;0.1% difference). cM/Mb uses an independently-sourced Ne (Han et al. 2024) rather than the paper's own calibrated figure.</t>
         </is>
@@ -637,33 +648,38 @@
           <t>Stevison et al. 2016 MBE</t>
         </is>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>10 individuals</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
         <v>0.7199</v>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>computed using independent Ne=27,795 (de Manuel et al. 2016 Science, per-subspecies long-term Ne from a whole-genome demographic model; value taken from Fontsere et al. 2022 Cell Genomics's own citation of de Manuel et al. 2016, since de Manuel's own Supplementary Materials tables were not directly obtained) — not the paper's own circular ~1.193 cM/Mb. Supersedes an earlier value using the Prado-Martinez et al. 2013 range midpoint (27,750) — nearly identical by coincidence, but now a genuine point estimate rather than a range midpoint</t>
         </is>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v>0.821</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>independent (raw/unbinned)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>ρ/kb = 0.8004</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>ρ/kb independently validated against the published value (&lt;0.1% difference). cM/Mb uses an independently-sourced Ne (de Manuel et al. 2016) rather than the paper's own calibrated figure.</t>
         </is>
@@ -700,33 +716,38 @@
           <t>Stevison et al. 2016 MBE</t>
         </is>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>15 individuals</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>0.7423999999999999</v>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Computed using an independent Ne=31,777 (McManus et al. 2015 MBE, ancestral/long-duration epoch of the best-fit 3-epoch ∂a∂i demographic model, same GAGP individuals) rather than the paper's own circular ~1.193 cM/Mb. A genuine point estimate from a dedicated demographic study -- specifically the long-term/ancestral epoch, appropriate for a historical LD-based signal -- was preferred over the midpoint of the wider Prado-Martinez et al. 2013 range (40,150).</t>
         </is>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="J4" s="3" t="n">
         <v>0.8119</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>independent (raw/unbinned)</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>ρ/kb = 0.9437</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>ρ/kb independently validated against the published value (&lt;0.1% difference). cM/Mb uses an independently-sourced Ne (McManus et al. 2015) rather than the paper's own calibrated figure.</t>
         </is>
@@ -765,35 +786,40 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>3 individuals (testis samples)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>raw counts only, not rate-normalized (see notes)</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>not applicable (method)</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>GCV = 227; NCO rate (Supp. Table 6, mean of 3 individuals) = 2.54×10⁻⁶ per bp (GT21 3.08 / GT22 1.95 / GT43 2.60, ×10⁻⁶)</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>CO = 215</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>n=3 individuals; verified against deposited data (exact match to the paper's Table 1). NCO rate from the paper's own Supplementary Table 6 (model-based estimate).</t>
         </is>
@@ -830,33 +856,38 @@
           <t>Auton et al. 2012 Science</t>
         </is>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>10 individuals</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>0.9931</v>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>computed using independent Ne=17,378 (de Manuel et al. 2016 Science, per-subspecies long-term Ne from a whole-genome demographic model; value taken from Fontsere et al. 2022 Cell Genomics's own citation of de Manuel et al. 2016) applied to this project's back-solved raw ρ/kb (0.6903, recovered from the paper's own Ne=11,413 cM/Mb via ρ/kb=cM/Mb×Ne/25000) — supersedes the paper's own Ne=11,413, which was itself calibrated assuming human/chimp map lengths are ~equal, not an independent demographic estimate. Now on the same non-circular Ne footing as the other 3 great-ape LD rows, so no longer excluded from the cross-clade baseline average</t>
         </is>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>0.7766</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>independent (raw/unbinned)</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>ρ/kb = 0.6903 (back-solved from paper's own Ne=11,413 cM/Mb)</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>Ne updated from the paper's own calibrated figure to an independently-sourced point estimate (de Manuel et al. 2016).</t>
         </is>
@@ -895,35 +926,40 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>4 individuals (testis samples)</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
           <t>raw counts only, not rate-normalized</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
           <t>not applicable (method)</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>GCV = 269; NCO rate (Supp. Table 6, mean of 4 individuals) = 1.86×10⁻⁶ per bp (CT15 1.26 / CT22 1.84 / CT28 2.36 / CT32 1.96, ×10⁻⁶)</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>CO = 495</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>n=4 individuals; verified against deposited data. NCO rate from the paper's own Supplementary Table 6 (model-based estimate).</t>
         </is>
@@ -960,33 +996,38 @@
           <t>Stevison, unpublished; now available in its own GitHub repo</t>
         </is>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>8 individuals</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
         <v>1.5498</v>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>computed; Ne=57,000, present-day NLE-specific (Veeramah et al. 2015 Genetics, ABC analysis; 95% CI 35,667-91,000 gives cM/Mb range 0.97-2.48) — cross-validated by an independent ~70k estimate August Woerner computed directly from this same dataset (email correspondence); supersedes an earlier ancestral pooled Ne=105,000 from Carbone et al. 2014</t>
         </is>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="J8" s="3" t="n">
         <v>0.8441</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>independent (raw/unbinned)</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>ρ/kb = 3.5335</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>Unpublished map (Stevison et al.); methods follow Stevison et al. 2016. Built from a VQSR-filtered VCF; 6 of 8 samples have lower sequencing coverage than the great-ape comparison studies.</t>
         </is>
@@ -1025,35 +1066,40 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>1 individual (testis sample)</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
           <t>raw counts only, not rate-normalized</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
           <t>not applicable (method)</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>GCV = 132; NCO rate (Supp. Table 6, sample LT39) = 3.48×10⁻⁶ per bp</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>CO = 70</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>n=1 individual; different genus than the Nomascus gibbon LD map elsewhere in this table. NCO rate from the paper's own Supplementary Table 6 (model-based estimate).</t>
         </is>
@@ -1090,35 +1136,40 @@
           <t>Pardo-Manuel de Villena &amp; Sapienza 2001 Mamm Genome</t>
         </is>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>not stated (compilation source; Dumont 2017 Table S1 also lists NA)</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="n">
         <v>0.8787</v>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>computed: 2,625 cM (52.5 XO x50 chiasma convention) / 2,987.40 Mb (autosomal-only, GCF_028858775.2, X 153.90 Mb + Y 36.45 Mb + MT excluded via NCBI sequence_reports)</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible (no fine-scale positions)</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>XO = 52.5</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>Subspecies attribution (western chimp) is a historical-plausibility inference, not a confirmed citation.</t>
         </is>
@@ -1155,33 +1206,38 @@
           <t>Wall, Robinson &amp; Cox 2022 GBE</t>
         </is>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>66 sequenced: 2 pedigrees (37 meioses: 20 paternal, 17 maternal) + 36 unrelated (LD map)</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
         <v>0.8851</v>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>LD map (pyrho) rescaled by authors to match own pedigree CO map length; recomputed total (2293.5 cM) matches published (2293 cM) to 0.02%</t>
         </is>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="J11" s="3" t="n">
         <v>0.7511</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>independent (raw/unbinned)</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>7.52×10⁻⁶ (paternal 5.34×10⁻⁶ / maternal 9.71×10⁻⁶)</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>842 COs</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>Strongest cross-validation case in this table: independently recomputed cM/Mb matches the paper's own reported value to within 0.02%.</t>
         </is>
@@ -1218,35 +1274,40 @@
           <t>Rogers et al. 2000 Genomics</t>
         </is>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>694 genotyped animals (12 pedigrees)</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="n">
         <v>0.9165</v>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>computed: 2,375 cM (paper's telomere-corrected total) ÷ 2,591.3 Mb (P. anubis physical length, cross-species approximation)</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible (no fine-scale positions)</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>2,375 cM</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>First-generation microsatellite linkage map; physical genome length borrowed from a congener (Papio anubis), since no P. hamadryas assembly exists.</t>
         </is>
@@ -1283,35 +1344,40 @@
           <t>Cox et al. 2006 Genomics</t>
         </is>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>984 genotyped animals (11 pedigrees)</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="n">
         <v>0.9085</v>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>Computed as 2,354 cM (paper's own raw/uncorrected total) ÷ 2,591.3 Mb (same cross-species approximation), for consistency with Dumont et al. 2017's independent compilation of this same map (their XO=47.08 uses the same raw 2,354 cM) rather than the telomere-corrected 2,754 cM figure.</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>2,354 cM</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>Second-generation microsatellite linkage map extending Rogers et al. (2000)'s pedigree; same congener substitution for physical length.</t>
         </is>
@@ -1350,35 +1416,40 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>1 individual (testis sample)</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
           <t>raw counts only, not rate-normalized</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
           <t>not applicable (method)</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>GCV = 40; NCO rate (Supp. Table 6, sample BT15) = 5.00×10⁻⁶ per bp</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>CO = 69</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>n=1 individual. NCO rate from the paper's own Supplementary Table 6 (model-based estimate).</t>
         </is>
@@ -1415,35 +1486,40 @@
           <t>Burt, Bell &amp; Harvey 1991 J Evol Biol (via Mank 2009)</t>
         </is>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>not stated (compilation source)</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="n">
         <v>0.7574</v>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>computed: sex-averaged 1.7825 XO/chromosome (female 1.5850, male 1.9800) × 20 bivalents × 50 cM convention = 1,782.5 cM ÷ 2,353.6 Mb (own species-specific chromosome-level assembly, GCA_028645565.1, autosomal only — chr21 (90.3 Mb) excluded as the inferred X, breaking the otherwise clean size-order of chromosomes 1-20; not an explicit NCBI X label, so flagged as inferred not confirmed)</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>XO (sex-averaged) = 35.65</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>Sex-averaged from Burt, Bell &amp; Harvey (1991), as compiled in Mank (2009) -- confirmed as a distinct source from the Macaca mulatta chiasma count elsewhere in this table (different original paper).</t>
         </is>
@@ -1480,35 +1556,40 @@
           <t>Versoza et al. 2024 GBE</t>
         </is>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>32 individuals (4 pedigrees), 7 paternal meioses</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>published (Table 1), male-only CO map</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
           <t>too sparse (165 autosomal COs) for fine-scale Lorenz curve</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>85 events; NCO rate (computed here) = 2.18×10⁻⁶ per bp per generation (paternal-only, 7 paternal meioses — the study's whole design), from 85 / (5,573,111 phase-informative sites × 7 meioses); the 5,573,111 figure is stated directly in the paper's main text (not a table), previously missed on the original extraction pass</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>165 COs, 2,357 cM male-only</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>See the companion LD row below: a separate paper (Terbot et al. 2025) cites this pedigree rate while describing it as that paper's own LD estimate -- a likely citation conflation in Terbot et al. 2025, not in this row's own source.</t>
         </is>
@@ -1545,33 +1626,38 @@
           <t>Versoza et al. 2024 GBE (companion map)</t>
         </is>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>11 individuals (pedigree parental generation)</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="n">
         <v>0.107</v>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>computed; not stated as a headline number in the paper itself</t>
         </is>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="J17" s="3" t="n">
         <v>0.6143999999999999</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>independent (raw/unbinned)</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>Terbot et al. (2025) cites "0.88 cM/Mb" as this paper's demography-aware LD estimate, but 0.88 is actually this same paper's pedigree rate (row above); this LD estimate is 0.107. Likely a citation error in Terbot et al. 2025.</t>
         </is>
@@ -1608,33 +1694,38 @@
           <t>Terbot, Calahorra-Oliart, Versoza et al. 2025 Am J Primatol</t>
         </is>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>79 individuals</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
         <v>0.6936</v>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>computed (published: 0.79 cM/Mb, ~12% higher — same direction paper's own simulations flag as pyrho's expected underestimation bias)</t>
         </is>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="J18" s="3" t="n">
         <v>0.2813</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>independent (raw/unbinned)</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
         <is>
           <t>Gini is notably lower than LDhat-based Gini elsewhere in this table (0.61-0.90 range) -- likely a pyrho block-penalty smoothing artifact rather than a real biological difference. See the bias-corrected row below (same study) for this population's representative estimate.</t>
         </is>
@@ -1671,35 +1762,40 @@
           <t>Terbot, Calahorra-Oliart, Versoza et al. 2025 Am J Primatol (bias-corrected estimate)</t>
         </is>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>79 individuals</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>paper's own stated bias-corrected estimate (p.8) — not independently computed by this project. Corrects for pyrho's known underestimation under this population's demographic history (severe contraction ~3,000 generations ago) plus gene-conversion effects, per the paper's own coalescent-simulation validation (Supporting Fig. 9) and citing Dutheil (2024)</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
           <t>see raw-pyrho row above (same study) for this population's Gini (0.2813)</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>The paper's own bias-corrected estimate, accounting for pyrho's known underestimation under this population's demographic history (a severe contraction ~3,000 generations ago).</t>
         </is>
@@ -1738,33 +1834,38 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
+          <t>123 individuals</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
           <t>0.448 ± 0.286</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>published (1Mb windows) — kept as primary despite Tier-2 upgrade; this project's own raw/unbinned recomputation (rho/kb=0.4877) is ~4.3x their stated rho=0.112, likely a binned-vs-raw discrepancy, not confirmed — see Xue_2020_macaque/RESULTS.md</t>
         </is>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="J20" s="3" t="n">
         <v>0.7944</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>independent (raw/unbinned, project standard; first numeric Gini for this species; Gini is scale-invariant so unaffected by the cM/Mb discrepancy above)</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>ρ = 0.112 ± 0.07 (4Neμ=0.0025, published); rho/kb=0.4877 (this project, raw/unbinned)</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>Independently recomputed raw/unbinned ρ/kb is ~4.3x higher than the paper's own stated value -- an unresolved raw-vs-binned discrepancy. The paper's own published cM/Mb is used here rather than the discrepant recomputed value.</t>
         </is>
@@ -1801,35 +1902,40 @@
           <t>Rogers et al. 2006 Genomics</t>
         </is>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>865 genotyped animals (5 pedigrees)</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="n">
         <v>0.698</v>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>computed: 2,048 cM ÷ 2,934.6 Mb (real chromosome-level assembly autosomal length, GCA_049350105.2, since 2006 paper predates a complete assembly)</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>2,048 cM (241 loci, 865 animals)</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>241 microsatellite loci; physical genome length uses a real chromosome-level assembly (this paper predates one).</t>
         </is>
@@ -1866,35 +1972,40 @@
           <t>Hassold et al. 2009 Cytogenet Genome Res</t>
         </is>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>11 individuals, 438 cells (via Dumont 2017 Table S1)</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>0.6645</v>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>computed: 1,950 cM (39.0 XO x50 MLH1 convention) / 2,934.6 Mb (autosomal-only, GCA_049350105.2, same figure already established for the Rogers 2006 and Burt/Mank rows elsewhere in this table -- no congener needed, own species already has this breakdown)</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>XO = 39.0</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="N22" s="3" t="inlineStr">
         <is>
           <t>Population/origin unspecified in the source compilation (Dumont et al. 2017 Table S1).</t>
         </is>
@@ -1931,35 +2042,40 @@
           <t>Pardo-Manuel de Villena &amp; Sapienza 2001 Mamm Genome</t>
         </is>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>not stated (compilation source; Dumont 2017 Table S1 also lists NA)</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="n">
         <v>0.6474</v>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>computed: 1,900 cM (38.0 XO x50 chiasma convention) / 2,934.6 Mb (autosomal-only, GCA_049350105.2, same figure as MLH1 row above)</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="M23" s="3" t="inlineStr">
         <is>
           <t>XO = 38.0</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="N23" s="3" t="inlineStr">
         <is>
           <t>Same source compilation as the MLH1 row above (Dumont et al. 2017 Table S1).</t>
         </is>
@@ -1996,35 +2112,40 @@
           <t>Burt, Bell &amp; Harvey 1991 J Evol Biol (via Mank 2009)</t>
         </is>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>not stated (compilation source)</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="n">
         <v>0.6909</v>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>computed: sex-averaged 2.0275 XO/chromosome (female 1.9800, male 2.0750) × 20 bivalents × 50 cM convention = 2,027.5 cM ÷ 2,934.6 Mb (autosomal-only, GCA_049350105.2, same figure as the corrected Rogers et al. 2006 row above)</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t>XO (sex-averaged) = 40.55</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="N24" s="3" t="inlineStr">
         <is>
           <t>Sex-averaged from Burt, Bell &amp; Harvey (1991), as compiled in Mank (2009) -- confirmed as a distinct source from the Pardo-Manuel de Villena &amp; Sapienza (2001) chiasma count elsewhere in this table.</t>
         </is>
@@ -2061,35 +2182,40 @@
           <t>Pardo-Manuel de Villena &amp; Sapienza 2001 Mamm Genome</t>
         </is>
       </c>
-      <c r="G25" s="3" t="n">
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>not stated (compilation source; Dumont 2017 Table S1 also lists NA)</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="n">
         <v>0.6938</v>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>computed: 2,000 cM (40.0 XO x50 chiasma convention) / 2,882.47 Mb (autosomal-only, GCF_043159975.1, X 159.76 Mb + Y 18.42 Mb excluded via NCBI sequence_reports)</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="M25" s="3" t="inlineStr">
         <is>
           <t>XO = 40.0</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t>This species' first cM/Mb value in this table; physical length uses this species' own chromosome-level assembly.</t>
         </is>
@@ -2128,35 +2254,40 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>1 individual (testis sample)</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
           <t>raw counts only, not rate-normalized</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
           <t>not applicable (method)</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>GCV = 131; NCO rate (Supp. Table 6, sample MT5) = 2.65×10⁻⁶ per bp</t>
         </is>
       </c>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t>CO = 171</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="N26" s="3" t="inlineStr">
         <is>
           <t>n=1 individual; different Macaca species than the M. mulatta rows above. NCO rate from the paper's own Supplementary Table 6 (model-based estimate).</t>
         </is>
@@ -2193,33 +2324,38 @@
           <t>Pfeifer 2020 MBE</t>
         </is>
       </c>
-      <c r="G27" s="3" t="n">
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>10 individuals</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="n">
         <v>0.4522</v>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>computed using paper's own Ne=17,085 (published: 0.434 ± 0.442, ~4% difference — strong validation)</t>
         </is>
       </c>
-      <c r="I27" s="3" t="n">
+      <c r="J27" s="3" t="n">
         <v>0.9523</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>independent (raw/unbinned)</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t>Highest raw/unbinned Gini in this table; independently corroborated by the paper's own Lorenz-curve figure and its statement that ~80% of recombination is concentrated in only 4% of the genome.</t>
         </is>
@@ -2256,35 +2392,40 @@
           <t>Jasinska et al. 2007 Mamm Genome</t>
         </is>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>434 genotyped animals (77 sub-pedigrees)</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="n">
         <v>1.0006</v>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>computed: 2,726 cM (raw, directly observed) ÷ 2,724.4 Mb (autosomal length, GCF_047675955.1, chromosome-level RefSeq assembly released Feb. 2025); extrapolated range 1.14-1.20 also reported in paper</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L28" s="3" t="inlineStr">
+      <c r="M28" s="3" t="inlineStr">
         <is>
           <t>2,726 cM (raw) / 3,112-3,282 cM (extrapolated)</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr">
+      <c r="N28" s="3" t="inlineStr">
         <is>
           <t>Physical genome length uses a real chromosome-level genome assembly rather than the LD map's own coverage-based estimate (the LD-based cM/Mb, row above, is unaffected by this correction).</t>
         </is>
@@ -2321,35 +2462,40 @@
           <t>Garcia-Cruz et al. 2009 BMC Genetics</t>
         </is>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>1 individual, 75 cells (via Dumont 2017 Table S1)</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="n">
         <v>0.7917999999999999</v>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>computed: 2,161 cM (43.22 MLH1 foci/cell x 50cM convention) / 2,729.2 Mb (Sapajus apella GCF_009761245.1, RefSeq reference genome, same genus under current taxonomy, TOTAL length -- not corrected, see note)</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L29" s="3" t="inlineStr">
+      <c r="M29" s="3" t="inlineStr">
         <is>
           <t>2,161 cM (43.22±5.38 MLH1 foci/cell, n=1 individual, 75 cells)</t>
         </is>
       </c>
-      <c r="M29" s="3" t="inlineStr">
+      <c r="N29" s="3" t="inlineStr">
         <is>
           <t>Predecessor paper to the Garcia-Cruz et al. 2011 rows below, same lab and method. Physical length uses a same-genus congener assembly (no chromosome-level Cebus/Sapajus assembly exists).</t>
         </is>
@@ -2386,35 +2532,40 @@
           <t>Garcia-Cruz et al. 2011 Chromosoma</t>
         </is>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>1 individual, 85 cells</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="n">
         <v>0.7598</v>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>computed: 2,065 cM (41.3 MLH1 foci/cell x 50cM convention) / 2,717.7 Mb (Cebus imitator GCF_001604975.1, RefSeq reference genome, same genus, TOTAL length -- not corrected, see note)</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible (single genome-wide count per cell, no positional data)</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="L30" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L30" s="3" t="inlineStr">
+      <c r="M30" s="3" t="inlineStr">
         <is>
           <t>2,065 cM (41.3±4.8 MLH1 foci/cell)</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
+      <c r="N30" s="3" t="inlineStr">
         <is>
           <t>Physical length uses a same-genus congener assembly (no chromosome-level Cebus/Sapajus assembly exists).</t>
         </is>
@@ -2451,35 +2602,40 @@
           <t>Garcia-Cruz et al. 2011 Chromosoma</t>
         </is>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>1 individual, 116 cells</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="n">
         <v>0.7212</v>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>computed: 1,960 cM / 2,717.7 Mb (same Cebus imitator reference as C. libidinosus, TOTAL length -- not corrected, see note)</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L31" s="3" t="inlineStr">
+      <c r="M31" s="3" t="inlineStr">
         <is>
           <t>1,960 cM (39.2±3.3 MLH1 foci/cell)</t>
         </is>
       </c>
-      <c r="M31" s="3" t="inlineStr">
+      <c r="N31" s="3" t="inlineStr">
         <is>
           <t>Physical length uses a same-genus congener assembly (no chromosome-level Cebus/Sapajus assembly exists).</t>
         </is>
@@ -2516,35 +2672,40 @@
           <t>Garcia-Cruz et al. 2011 Chromosoma</t>
         </is>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>1 individual, 165 cells</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="n">
         <v>0.7747000000000001</v>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>computed: 2,030 cM / 2,620.4 Mb (Alouatta juara GCA_963574365.1 - closest available congener; A. palliata, the only other assembled Alouatta, is more divergent Central American; TOTAL length -- not corrected, see note)</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
+      <c r="M32" s="3" t="inlineStr">
         <is>
           <t>2,030 cM (40.6±4.3 MLH1 foci/cell)</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
+      <c r="N32" s="3" t="inlineStr">
         <is>
           <t>Physical length uses a scaffold-level congener assembly (no chromosome-level Atelidae assembly exists anywhere), so the denominator is total-genome rather than autosome-only -- likely a modest underestimate of the true rate.</t>
         </is>
@@ -2581,33 +2742,38 @@
           <t>Soni, Versoza et al. 2025/26 bioRxiv (PREPRINT, not peer-reviewed)</t>
         </is>
       </c>
-      <c r="G33" s="3" t="n">
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>15 individuals</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="n">
         <v>0.91</v>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>published number only — paper never states the empirical Ne/θ used, so cM/Mb here is NOT independently validated (Ne back-solved ≈18,129 purely for transparency)</t>
         </is>
       </c>
-      <c r="I33" s="3" t="n">
+      <c r="J33" s="3" t="n">
         <v>0.8068</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>independent (raw/unbinned, scale-invariant so doesn't depend on missing Ne)</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="M33" s="3" t="inlineStr">
         <is>
           <t>ρ/kb = 1.1497 (raw, pre-conversion)</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
+      <c r="N33" s="3" t="inlineStr">
         <is>
           <t>Preprint as of this table's compilation. Companion pyrho estimate in the same paper is substantially lower (0.25 cM/Mb), consistent with a pyrho underestimation pattern seen elsewhere in this table.</t>
         </is>
@@ -2644,33 +2810,38 @@
           <t>Soni, Versoza et al. 2026 Heredity</t>
         </is>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>6 individuals</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="n">
         <v>0.9366</v>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>computed (published: 0.975, ~4% higher); rescaled by authors to match companion pedigree map length (2450 cM)</t>
         </is>
       </c>
-      <c r="I34" s="3" t="n">
+      <c r="J34" s="3" t="n">
         <v>0.8968</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>independent (raw/unbinned, finest available = 1kb bins)</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
         <is>
           <t>Recommended primary LD estimate for this species (closer fit to the companion pedigree map than the LDhat estimate below).</t>
         </is>
@@ -2707,33 +2878,38 @@
           <t>Soni, Versoza et al. 2026 Heredity</t>
         </is>
       </c>
-      <c r="G35" s="3" t="n">
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>6 individuals</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="n">
         <v>0.8239</v>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>computed (published: 0.978, ~16% higher — larger gap than LDhelmet, not fully explained, see notes)</t>
         </is>
       </c>
-      <c r="I35" s="3" t="n">
+      <c r="J35" s="3" t="n">
         <v>0.6025</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>independent (raw/unbinned)</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="L35" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
         <is>
           <t>Secondary/comparison LD estimator alongside LDhelmet above.</t>
         </is>
@@ -2770,35 +2946,40 @@
           <t>Versoza et al. 2026 GBE</t>
         </is>
       </c>
-      <c r="G36" s="3" t="n">
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>17 individuals (3 families), 22 meioses (11 maternal, 11 paternal)</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>published (Table 1), sex-averaged (male 1.04 / female 1.00)</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
           <t>too sparse (269.5 avg COs) for fine-scale Lorenz curve — use companion LD Gini instead</t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
+      <c r="L36" s="3" t="inlineStr">
         <is>
           <t>184 events (101 maternal / 83 paternal); NCO rate (computed here) = 3.95×10⁻⁶ per bp per generation sex-avg (maternal 4.20×10⁻⁶ / paternal 3.69×10⁻⁶), from per-family phase-informative marker counts in Supplementary Table 3 -- 101/24,021,582 maternal site-meioses and 83/22,522,884 paternal site-meioses, pooled</t>
         </is>
       </c>
-      <c r="L36" s="3" t="inlineStr">
+      <c r="M36" s="3" t="inlineStr">
         <is>
           <t>269.5 COs (male 274 / female 265), 2,450 cM sex-avg</t>
         </is>
       </c>
-      <c r="M36" s="3" t="inlineStr">
+      <c r="N36" s="3" t="inlineStr">
         <is>
           <t>The pedigree map the companion LD estimates (rows above) were rescaled to match.</t>
         </is>
@@ -2835,33 +3016,38 @@
           <t>Soni, Versoza et al. 2025 Ecology and Evolution</t>
         </is>
       </c>
-      <c r="G37" s="3" t="n">
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>5 individuals</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="n">
         <v>0.6692</v>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>computed (published: 0.68, ~2% difference — strong validation); deposited data was pre-rescaling, factor of 14.444 applied per paper's stated methodology</t>
         </is>
       </c>
-      <c r="I37" s="3" t="n">
+      <c r="J37" s="3" t="n">
         <v>0.4509</v>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>independent (raw/unbinned, scale-invariant)</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="L37" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
         <is>
           <t>Rescaled to match the companion pedigree study's map length, following the same procedure used for Papio anubis above.</t>
         </is>
@@ -2898,35 +3084,40 @@
           <t>Versoza et al. 2025 GBE</t>
         </is>
       </c>
-      <c r="G38" s="3" t="n">
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>14 individuals, 20 meioses (10 maternal, 10 paternal)</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr">
         <is>
           <t>published (Table 1), sex-averaged (male 0.77 / female 0.94)</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
           <t>too sparse (152.5 avg COs) — use companion LD Gini instead</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
+      <c r="L38" s="3" t="inlineStr">
         <is>
           <t>6.8×10⁻⁷ (female 6.4×10⁻⁷ / male 7.4×10⁻⁷)</t>
         </is>
       </c>
-      <c r="L38" s="3" t="inlineStr">
+      <c r="M38" s="3" t="inlineStr">
         <is>
           <t>152.5 COs (male 142 / female 163), 1,525 cM sex-avg</t>
         </is>
       </c>
-      <c r="M38" s="3" t="inlineStr">
+      <c r="N38" s="3" t="inlineStr">
         <is>
           <t>The pedigree map the companion LD estimate (row above) was rescaled to match.</t>
         </is>
@@ -2963,35 +3154,40 @@
           <t>Segura et al. 2013 Proc R Soc B</t>
         </is>
       </c>
-      <c r="G39" s="3" t="n">
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>1 individual, 49 cells (via Dumont 2017 Table S1)</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>0.667</v>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>computed: 1,845 cM (36.9 XO x50) / 2,765.92 Mb (autosomal-only, Callithrix jacchus congener GCF_049354715.1, X 151.63 Mb + Y 15.86 Mb + MT excluded via NCBI sequence_reports -- own genus Cebuella has no chromosome-level assembly; Cebuella was until recently classified within Callithrix, making this an unusually close cross-genus substitute)</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="L39" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L39" s="3" t="inlineStr">
+      <c r="M39" s="3" t="inlineStr">
         <is>
           <t>1,845 cM (36.9 MLH1 foci/cell)</t>
         </is>
       </c>
-      <c r="M39" s="3" t="inlineStr">
+      <c r="N39" s="3" t="inlineStr">
         <is>
           <t>Physical length uses a same-family congener (Callithrix jacchus) -- no chromosome-level Cebuella assembly exists; Cebuella was until recently classified within Callithrix.</t>
         </is>
@@ -3028,35 +3224,40 @@
           <t>Pardo-Manuel de Villena &amp; Sapienza 2001 Mamm Genome</t>
         </is>
       </c>
-      <c r="G40" s="3" t="n">
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>not stated (compilation source; Dumont 2017 Table S1 also lists NA)</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="n">
         <v>0.7538</v>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>computed: 2,085 cM (41.7 XO x50) / 2,765.92 Mb (same autosomal-only congener figure as MLH1 row above)</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K40" s="3" t="inlineStr">
+      <c r="L40" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L40" s="3" t="inlineStr">
+      <c r="M40" s="3" t="inlineStr">
         <is>
           <t>2,085 cM (41.7 chiasmata/cell)</t>
         </is>
       </c>
-      <c r="M40" s="3" t="inlineStr">
+      <c r="N40" s="3" t="inlineStr">
         <is>
           <t>Second, independent cytogenetic method for the same species/individual pool as the MLH1 row above; same congener-based physical length.</t>
         </is>
@@ -3093,35 +3294,40 @@
           <t>Pardo-Manuel de Villena &amp; Sapienza 2001 Mamm Genome</t>
         </is>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>not stated (compilation source; Dumont 2017 Table S1 also lists NA)</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="n">
         <v>0.7451</v>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>computed: 2,025 cM (40.5 XO x50) / 2,717.70 Mb (Cebus imitator congener, GCF_001604975.1 -- same substitution already used for this project's other 3 Cebus/Sapajus species; TOTAL length -- not corrected, see note)</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K41" s="3" t="inlineStr">
+      <c r="L41" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L41" s="3" t="inlineStr">
+      <c r="M41" s="3" t="inlineStr">
         <is>
           <t>2,025 cM (40.5 chiasmata/cell)</t>
         </is>
       </c>
-      <c r="M41" s="3" t="inlineStr">
+      <c r="N41" s="3" t="inlineStr">
         <is>
           <t>Physical length uses a same-genus congener assembly (no chromosome-level Cebus/Sapajus assembly exists).</t>
         </is>
@@ -3158,35 +3364,40 @@
           <t>Pardo-Manuel de Villena &amp; Sapienza 2001 Mamm Genome</t>
         </is>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>not stated (compilation source; Dumont 2017 Table S1 also lists NA)</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="n">
         <v>0.6253</v>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
         <is>
           <t>computed: 1,835 cM (36.7 XO x50) / 2,934.6 Mb (autosomal-only, Macaca mulatta congener GCF_049350105.2 -- own species' assembly, GCA_963573635.1, is scaffold-level; mulatta is the closest chromosome-level relative, same 'sinica' species group)</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K42" s="3" t="inlineStr">
+      <c r="L42" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L42" s="3" t="inlineStr">
+      <c r="M42" s="3" t="inlineStr">
         <is>
           <t>1,835 cM (36.7 chiasmata/cell)</t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr">
+      <c r="N42" s="3" t="inlineStr">
         <is>
           <t>Physical length uses a same-genus congener assembly (Macaca mulatta), since no chromosome-level M. fuscata assembly exists.</t>
         </is>
@@ -3223,35 +3434,40 @@
           <t>Burt &amp; Bell 1987 Nature</t>
         </is>
       </c>
-      <c r="G43" s="3" t="n">
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>not stated (compilation source; Dumont 2017 Table S1 also lists NA)</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="n">
         <v>0.6765</v>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="I43" s="3" t="inlineStr">
         <is>
           <t>computed: 1,950 cM (39.0 XO x50) / 2,882.47 Mb (autosomal-only, Macaca nemestrina congener GCF_043159975.1 -- own species' assembly, GCA_963573485.1, is scaffold-level; nemestrina is the closest chromosome-level relative, same 'silenus-sylvanus' species group as the Sulawesi macaques including nigra, a closer phylogenetic match than mulatta)</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K43" s="3" t="inlineStr">
+      <c r="L43" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L43" s="3" t="inlineStr">
+      <c r="M43" s="3" t="inlineStr">
         <is>
           <t>1,950 cM (39.0 chiasmata/cell)</t>
         </is>
       </c>
-      <c r="M43" s="3" t="inlineStr">
+      <c r="N43" s="3" t="inlineStr">
         <is>
           <t>Physical length uses a same-genus congener assembly (Macaca nemestrina, phylogenetically closer than M. mulatta), since no chromosome-level M. nigra assembly exists.</t>
         </is>
@@ -3288,35 +3504,40 @@
           <t>Pardo-Manuel de Villena &amp; Sapienza 2001 Mamm Genome</t>
         </is>
       </c>
-      <c r="G44" s="3" t="n">
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>not stated (compilation source; Dumont 2017 Table S1 also lists NA)</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="n">
         <v>0.7866</v>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="I44" s="3" t="inlineStr">
         <is>
           <t>computed: 2,250 cM (45.0 XO x50) / 2,860.58 Mb (own assembly, GCA_004802615.1, TOTAL length -- not corrected, see note)</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K44" s="3" t="inlineStr">
+      <c r="L44" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L44" s="3" t="inlineStr">
+      <c r="M44" s="3" t="inlineStr">
         <is>
           <t>2,250 cM (45.0 chiasmata/cell)</t>
         </is>
       </c>
-      <c r="M44" s="3" t="inlineStr">
+      <c r="N44" s="3" t="inlineStr">
         <is>
           <t>Physical length uses this species' own (scaffold-level) assembly; no chromosome-level Mandrillus assembly exists for a congener substitution, so the denominator is total-genome rather than autosome-only -- likely a modest underestimate of the true rate.</t>
         </is>
@@ -3353,35 +3574,40 @@
           <t>Segura et al. 2013 Proc R Soc B</t>
         </is>
       </c>
-      <c r="G45" s="3" t="n">
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>1 individual, 60 cells (via Dumont 2017 Table S1)</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="n">
         <v>0.6685</v>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t>computed: 1,985 cM (39.7 XO x50) / 2,969.30 Mb (own assembly, GCA_028551445.1)</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K45" s="3" t="inlineStr">
+      <c r="L45" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L45" s="3" t="inlineStr">
+      <c r="M45" s="3" t="inlineStr">
         <is>
           <t>1,985 cM (39.7 MLH1 foci/cell)</t>
         </is>
       </c>
-      <c r="M45" s="3" t="inlineStr">
+      <c r="N45" s="3" t="inlineStr">
         <is>
           <t>Physical length uses this species' own assembly; the X chromosome could not be confidently identified in this assembly, so an autosome-only correction was not possible.</t>
         </is>
@@ -3418,35 +3644,40 @@
           <t>Segura et al. 2013 Proc R Soc B</t>
         </is>
       </c>
-      <c r="G46" s="3" t="n">
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>1 individual, 76 cells (via Dumont 2017 Table S1)</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="n">
         <v>0.8579</v>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>computed: 1,795 cM (35.9 XO x50) / 2,092.34 Mb (autosomal-only, GCF_020740605.2, X 73.53 Mb + Y 6.80 Mb excluded via NCBI sequence_reports)</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
+      <c r="L46" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L46" s="3" t="inlineStr">
+      <c r="M46" s="3" t="inlineStr">
         <is>
           <t>1,795 cM (35.9 MLH1 foci/cell)</t>
         </is>
       </c>
-      <c r="M46" s="3" t="inlineStr">
+      <c r="N46" s="3" t="inlineStr">
         <is>
           <t>First non-aye-aye Lemuridae species in this table. Physical length uses this species' own chromosome-level assembly.</t>
         </is>
@@ -3483,35 +3714,40 @@
           <t>Pardo-Manuel de Villena &amp; Sapienza 2001 Mamm Genome</t>
         </is>
       </c>
-      <c r="G47" s="3" t="n">
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>not stated (compilation source; Dumont 2017 Table S1 also lists NA)</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="n">
         <v>0.8508</v>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="I47" s="3" t="inlineStr">
         <is>
           <t>computed: 1,815 cM (36.3 XO x50) / 2,133.22 Mb (own assembly, GCA_963573725.1 -- note this 2023 PGDP assembly is ~600Mb smaller than an older 2019 assembly for the same subspecies, unresolved discrepancy, see Dumont2017_CO_assurance/RESULTS.md)</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K47" s="3" t="inlineStr">
+      <c r="L47" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L47" s="3" t="inlineStr">
+      <c r="M47" s="3" t="inlineStr">
         <is>
           <t>1,815 cM (36.3 chiasmata/cell)</t>
         </is>
       </c>
-      <c r="M47" s="3" t="inlineStr">
+      <c r="N47" s="3" t="inlineStr">
         <is>
           <t>Now classified as Eulemur fulvus under current taxonomy.</t>
         </is>
@@ -3548,35 +3784,40 @@
           <t>Pardo-Manuel de Villena &amp; Sapienza 2001 Mamm Genome</t>
         </is>
       </c>
-      <c r="G48" s="3" t="n">
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>not stated (compilation source; Dumont 2017 Table S1 also lists NA)</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="n">
         <v>0.825</v>
       </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr">
         <is>
           <t>computed: 1,760 cM (35.2 XO x50) / 2,133.22 Mb (nominate E. fulvus assembly -- no subspecies-specific assembly exists)</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K48" s="3" t="inlineStr">
+      <c r="L48" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L48" s="3" t="inlineStr">
+      <c r="M48" s="3" t="inlineStr">
         <is>
           <t>1,760 cM (35.2 chiasmata/cell)</t>
         </is>
       </c>
-      <c r="M48" s="3" t="inlineStr">
+      <c r="N48" s="3" t="inlineStr">
         <is>
           <t>Subspecies-level karyotype variant (2N=48 vs. nominate 2N=60).</t>
         </is>
@@ -3613,35 +3854,40 @@
           <t>Pardo-Manuel de Villena &amp; Sapienza 2001 Mamm Genome</t>
         </is>
       </c>
-      <c r="G49" s="3" t="n">
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>not stated (compilation source; Dumont 2017 Table S1 also lists NA)</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="n">
         <v>0.8476</v>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="I49" s="3" t="inlineStr">
         <is>
           <t>computed: 1,800 cM (36.0 XO x50) / 2,123.59 Mb (own subspecies-matched assembly, GCA_963575015.1)</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K49" s="3" t="inlineStr">
+      <c r="L49" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L49" s="3" t="inlineStr">
+      <c r="M49" s="3" t="inlineStr">
         <is>
           <t>1,800 cM (36.0 chiasmata/cell)</t>
         </is>
       </c>
-      <c r="M49" s="3" t="inlineStr">
+      <c r="N49" s="3" t="inlineStr">
         <is>
           <t>Subspecies-level karyotype variant (2N=50).</t>
         </is>
@@ -3678,35 +3924,40 @@
           <t>Segura et al. 2013 Proc R Soc B</t>
         </is>
       </c>
-      <c r="G50" s="3" t="n">
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>1 individual, 105 cells (via Dumont 2017 Table S1)</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="n">
         <v>0.6807</v>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="I50" s="3" t="inlineStr">
         <is>
           <t>computed: 1,945 cM (38.9 XO x50) / 2,857.31 Mb (autosomal-only, GCA_031835075.1, X 148.49 Mb excluded via NCBI sequence_reports; 2 haplotype-resolved 2026 assemblies exist for this species but were not used -- a single haplotype isn't a genome-length estimate, see Dumont2017_CO_assurance/RESULTS.md)</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K50" s="3" t="inlineStr">
+      <c r="L50" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L50" s="3" t="inlineStr">
+      <c r="M50" s="3" t="inlineStr">
         <is>
           <t>1,945 cM (38.9 MLH1 foci/cell)</t>
         </is>
       </c>
-      <c r="M50" s="3" t="inlineStr">
+      <c r="N50" s="3" t="inlineStr">
         <is>
           <t>Physical length uses this species' own chromosome-level assembly, autosome-only.</t>
         </is>
@@ -3743,42 +3994,47 @@
           <t>Pardo-Manuel de Villena &amp; Sapienza 2001 Mamm Genome</t>
         </is>
       </c>
-      <c r="G51" s="3" t="n">
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>not stated (compilation source; Dumont 2017 Table S1 also lists NA)</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="n">
         <v>0.6929999999999999</v>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>computed: 1,980 cM (39.6 XO x50) / 2,857.31 Mb (same autosomal-only assembly figure as MLH1 row above)</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
           <t>structurally impossible</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr">
+      <c r="L51" s="3" t="inlineStr">
         <is>
           <t>n/a (method)</t>
         </is>
       </c>
-      <c r="L51" s="3" t="inlineStr">
+      <c r="M51" s="3" t="inlineStr">
         <is>
           <t>1,980 cM (39.6 chiasmata/cell)</t>
         </is>
       </c>
-      <c r="M51" s="3" t="inlineStr">
+      <c r="N51" s="3" t="inlineStr">
         <is>
           <t>Second, independent cytogenetic method for the same species; same physical length as the MLH1 row above.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M51"/>
+  <autoFilter ref="A1:N51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
